--- a/docs/StructureDefinition-PASportServiceRequest.xlsx
+++ b/docs/StructureDefinition-PASportServiceRequest.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T05:34:23+08:00</t>
+    <t>2026-02-28T07:16:04+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PASportServiceRequest.xlsx
+++ b/docs/StructureDefinition-PASportServiceRequest.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T07:16:04+08:00</t>
+    <t>2026-02-28T23:13:53+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PASportServiceRequest.xlsx
+++ b/docs/StructureDefinition-PASportServiceRequest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.1</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T23:13:53+08:00</t>
+    <t>2026-03-01T19:25:35+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PASportServiceRequest.xlsx
+++ b/docs/StructureDefinition-PASportServiceRequest.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T19:25:35+08:00</t>
+    <t>2026-03-02T02:26:08+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PASportServiceRequest.xlsx
+++ b/docs/StructureDefinition-PASportServiceRequest.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T02:26:08+08:00</t>
+    <t>2026-04-02T13:32:15+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -371,7 +371,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -706,7 +706,7 @@
     <t>ServiceRequest.instantiatesCanonical</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(ActivityDefinition|PlanDefinition)
+    <t xml:space="preserve">canonical(ActivityDefinition|4.0.1|PlanDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -908,7 +908,7 @@
     <t>Classification of the requested service.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/servicerequest-category</t>
+    <t>http://hl7.org/fhir/ValueSet/servicerequest-category|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">pattern:$this}
@@ -958,14 +958,10 @@
     <t>CodeableConcept.coding</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>CE/CNE/CWE subset one of the sets of component 1-3 or 4-6</t>
-  </si>
-  <si>
-    <t>CV</t>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
   </si>
   <si>
     <t>ServiceRequest.category.coding.id</t>
@@ -1201,13 +1197,13 @@
 </t>
   </si>
   <si>
-    <t>概念（Concept）— 參照一個專門術語或只是文字表述</t>
-  </si>
-  <si>
-    <t>A concept that may be defined by a formal reference to a terminology or ontology or may be provided by text.</t>
-  </si>
-  <si>
-    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
+    <t>What is being requested/ordered</t>
+  </si>
+  <si>
+    <t>A code that identifies a particular service (i.e., procedure, diagnostic investigation, or panel of investigations) that have been requested.</t>
+  </si>
+  <si>
+    <t>Many laboratory and radiology procedure codes embed the specimen/organ system in the test order name, for example,  serum or serum/plasma glucose, or a chest x-ray. The specimen might not be recorded separately from the test code.</t>
   </si>
   <si>
     <t>此資料項目實作者可視實務專案需求只綁定以下slices中的任一值集。</t>
@@ -1216,10 +1212,19 @@
     <t>http://hl7.org/fhir/ValueSet/procedure-code</t>
   </si>
   <si>
-    <t>CE/CNE/CWE</t>
-  </si>
-  <si>
-    <t>CD</t>
+    <t>Request.code</t>
+  </si>
+  <si>
+    <t>PR1-3 / OBR-4  (varies by domain)</t>
+  </si>
+  <si>
+    <t>.code</t>
+  </si>
+  <si>
+    <t>FiveWs.what[x]</t>
+  </si>
+  <si>
+    <t>Procedure.procedureCode</t>
   </si>
   <si>
     <t>ServiceRequest.code.id</t>
@@ -1391,7 +1396,7 @@
     <t>Codified order entry details which are based on order context.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/servicerequest-orderdetail</t>
+    <t>http://hl7.org/fhir/ValueSet/servicerequest-orderdetail|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">prr-1
@@ -1401,12 +1406,6 @@
     <t>NTE</t>
   </si>
   <si>
-    <t>.code</t>
-  </si>
-  <si>
-    <t>Procedure.procedureCode</t>
-  </si>
-  <si>
     <t>ServiceRequest.quantity[x]</t>
   </si>
   <si>
@@ -1534,7 +1533,7 @@
     <t>A coded concept identifying the pre-condition that should hold prior to performing a procedure.  For example "pain", "on flare-up", etc.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-as-needed-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-as-needed-reason|4.0.1</t>
   </si>
   <si>
     <t>boolean: precondition.negationInd (inversed - so negationInd = true means asNeeded=false CodeableConcept: precondition.observationEventCriterion[code="Assertion"].value</t>
@@ -1629,7 +1628,7 @@
     <t>Indicates specific responsibility of an individual within the care team, such as "Primary physician", "Team coordinator", "Caregiver", etc.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/participant-role</t>
+    <t>http://hl7.org/fhir/ValueSet/participant-role|4.0.1</t>
   </si>
   <si>
     <t>Request.performerType</t>
@@ -1785,7 +1784,7 @@
 AOE</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1851,7 +1850,7 @@
     <t>Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>targetSiteCode</t>
@@ -1894,7 +1893,7 @@
     <t>ServiceRequest.relevantHistory</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Provenance)
+    <t xml:space="preserve">Reference(Provenance|4.0.1)
 </t>
   </si>
   <si>
@@ -5694,7 +5693,7 @@
         <v>20</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
         <v>297</v>
@@ -5767,7 +5766,7 @@
         <v>80</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>303</v>
+        <v>20</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>101</v>
@@ -5776,10 +5775,10 @@
         <v>20</v>
       </c>
       <c r="AL30" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AM30" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>20</v>
@@ -5790,10 +5789,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5822,7 +5821,7 @@
         <v>292</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5905,10 +5904,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5937,10 +5936,10 @@
         <v>295</v>
       </c>
       <c r="M32" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="N32" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>310</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6022,10 +6021,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6051,65 +6050,65 @@
         <v>103</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="N33" t="s" s="2">
+      <c r="O33" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="S33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF33" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="S33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF33" t="s" s="2">
-        <v>317</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -6127,10 +6126,10 @@
         <v>20</v>
       </c>
       <c r="AL33" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="AM33" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>319</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>20</v>
@@ -6141,10 +6140,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6170,13 +6169,13 @@
         <v>157</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>323</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6226,7 +6225,7 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -6244,10 +6243,10 @@
         <v>20</v>
       </c>
       <c r="AL34" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="AM34" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>20</v>
@@ -6258,10 +6257,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6287,63 +6286,63 @@
         <v>109</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>329</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="S35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF35" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="S35" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T35" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U35" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V35" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W35" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X35" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y35" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z35" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA35" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB35" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD35" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE35" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF35" t="s" s="2">
-        <v>332</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -6361,10 +6360,10 @@
         <v>20</v>
       </c>
       <c r="AL35" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="AM35" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>20</v>
@@ -6375,10 +6374,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6404,14 +6403,14 @@
         <v>157</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>20</v>
@@ -6460,7 +6459,7 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -6478,10 +6477,10 @@
         <v>20</v>
       </c>
       <c r="AL36" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="AM36" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>341</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>20</v>
@@ -6492,10 +6491,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6518,19 +6517,19 @@
         <v>90</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="N37" t="s" s="2">
+      <c r="O37" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>20</v>
@@ -6579,7 +6578,7 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6597,10 +6596,10 @@
         <v>20</v>
       </c>
       <c r="AL37" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AM37" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>20</v>
@@ -6611,10 +6610,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6640,16 +6639,16 @@
         <v>157</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="N38" t="s" s="2">
+      <c r="O38" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>20</v>
@@ -6698,7 +6697,7 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6716,10 +6715,10 @@
         <v>20</v>
       </c>
       <c r="AL38" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AM38" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>20</v>
@@ -6730,13 +6729,13 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>279</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>20</v>
@@ -6798,10 +6797,10 @@
         <v>173</v>
       </c>
       <c r="Y39" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="Z39" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="Z39" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>20</v>
@@ -6851,10 +6850,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6880,10 +6879,10 @@
         <v>109</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6891,7 +6890,7 @@
         <v>20</v>
       </c>
       <c r="Q40" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="R40" t="s" s="2">
         <v>20</v>
@@ -6915,11 +6914,11 @@
         <v>173</v>
       </c>
       <c r="Y40" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="Z40" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="Z40" t="s" s="2">
-        <v>368</v>
-      </c>
       <c r="AA40" t="s" s="2">
         <v>20</v>
       </c>
@@ -6936,7 +6935,7 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6951,16 +6950,16 @@
         <v>101</v>
       </c>
       <c r="AK40" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="AL40" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="AL40" t="s" s="2">
+      <c r="AM40" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="AM40" t="s" s="2">
+      <c r="AN40" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>20</v>
@@ -6968,10 +6967,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6994,26 +6993,26 @@
         <v>90</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="N41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="O41" t="s" s="2">
+      <c r="P41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q41" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="P41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q41" t="s" s="2">
-        <v>378</v>
-      </c>
       <c r="R41" t="s" s="2">
         <v>20</v>
       </c>
@@ -7057,7 +7056,7 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -7072,13 +7071,13 @@
         <v>101</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM41" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="AL41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>20</v>
@@ -7089,14 +7088,14 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -7112,19 +7111,19 @@
         <v>20</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="K42" t="s" s="2">
         <v>280</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>384</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>385</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7153,11 +7152,11 @@
         <v>285</v>
       </c>
       <c r="Y42" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="Z42" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="Z42" t="s" s="2">
-        <v>387</v>
-      </c>
       <c r="AA42" t="s" s="2">
         <v>20</v>
       </c>
@@ -7174,7 +7173,7 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -7183,13 +7182,13 @@
         <v>89</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>303</v>
+        <v>20</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>20</v>
+        <v>387</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>388</v>
@@ -7198,18 +7197,18 @@
         <v>389</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>20</v>
+        <v>390</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>20</v>
+        <v>391</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7321,10 +7320,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7436,10 +7435,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7459,7 +7458,7 @@
         <v>20</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="K45" t="s" s="2">
         <v>297</v>
@@ -7530,7 +7529,7 @@
         <v>80</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>303</v>
+        <v>20</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>101</v>
@@ -7539,10 +7538,10 @@
         <v>20</v>
       </c>
       <c r="AL45" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AM45" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>20</v>
@@ -7553,13 +7552,13 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="D46" t="s" s="2">
         <v>20</v>
@@ -7578,7 +7577,7 @@
         <v>20</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="K46" t="s" s="2">
         <v>297</v>
@@ -7622,7 +7621,7 @@
       </c>
       <c r="Y46" s="2"/>
       <c r="Z46" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>20</v>
@@ -7649,7 +7648,7 @@
         <v>80</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>303</v>
+        <v>20</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>101</v>
@@ -7658,10 +7657,10 @@
         <v>20</v>
       </c>
       <c r="AL46" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AM46" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>20</v>
@@ -7672,13 +7671,13 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>20</v>
@@ -7697,7 +7696,7 @@
         <v>20</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="K47" t="s" s="2">
         <v>297</v>
@@ -7741,7 +7740,7 @@
       </c>
       <c r="Y47" s="2"/>
       <c r="Z47" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>20</v>
@@ -7768,7 +7767,7 @@
         <v>80</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>303</v>
+        <v>20</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>101</v>
@@ -7777,10 +7776,10 @@
         <v>20</v>
       </c>
       <c r="AL47" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AM47" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>20</v>
@@ -7791,13 +7790,13 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="D48" t="s" s="2">
         <v>20</v>
@@ -7816,7 +7815,7 @@
         <v>20</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="K48" t="s" s="2">
         <v>297</v>
@@ -7860,7 +7859,7 @@
       </c>
       <c r="Y48" s="2"/>
       <c r="Z48" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>20</v>
@@ -7887,7 +7886,7 @@
         <v>80</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>303</v>
+        <v>20</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>101</v>
@@ -7896,10 +7895,10 @@
         <v>20</v>
       </c>
       <c r="AL48" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AM48" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="AM48" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>20</v>
@@ -7910,13 +7909,13 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="D49" t="s" s="2">
         <v>20</v>
@@ -7935,7 +7934,7 @@
         <v>20</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="K49" t="s" s="2">
         <v>297</v>
@@ -7979,7 +7978,7 @@
       </c>
       <c r="Y49" s="2"/>
       <c r="Z49" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>20</v>
@@ -8006,7 +8005,7 @@
         <v>80</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>303</v>
+        <v>20</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>101</v>
@@ -8015,10 +8014,10 @@
         <v>20</v>
       </c>
       <c r="AL49" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AM49" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>20</v>
@@ -8029,13 +8028,13 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="D50" t="s" s="2">
         <v>20</v>
@@ -8054,7 +8053,7 @@
         <v>20</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="K50" t="s" s="2">
         <v>297</v>
@@ -8098,7 +8097,7 @@
       </c>
       <c r="Y50" s="2"/>
       <c r="Z50" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>20</v>
@@ -8125,7 +8124,7 @@
         <v>80</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>303</v>
+        <v>20</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>101</v>
@@ -8134,10 +8133,10 @@
         <v>20</v>
       </c>
       <c r="AL50" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AM50" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>20</v>
@@ -8148,13 +8147,13 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>20</v>
@@ -8173,7 +8172,7 @@
         <v>20</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="K51" t="s" s="2">
         <v>297</v>
@@ -8217,7 +8216,7 @@
       </c>
       <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>20</v>
@@ -8244,7 +8243,7 @@
         <v>80</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>303</v>
+        <v>20</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>101</v>
@@ -8253,10 +8252,10 @@
         <v>20</v>
       </c>
       <c r="AL51" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AM51" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>20</v>
@@ -8267,13 +8266,13 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D52" t="s" s="2">
         <v>20</v>
@@ -8292,7 +8291,7 @@
         <v>20</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="K52" t="s" s="2">
         <v>297</v>
@@ -8336,7 +8335,7 @@
       </c>
       <c r="Y52" s="2"/>
       <c r="Z52" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>20</v>
@@ -8363,7 +8362,7 @@
         <v>80</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>303</v>
+        <v>20</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>101</v>
@@ -8372,10 +8371,10 @@
         <v>20</v>
       </c>
       <c r="AL52" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AM52" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>20</v>
@@ -8386,10 +8385,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8418,7 +8417,7 @@
         <v>292</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8501,10 +8500,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8533,10 +8532,10 @@
         <v>295</v>
       </c>
       <c r="M54" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="N54" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>310</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8618,10 +8617,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8647,16 +8646,16 @@
         <v>103</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="N55" t="s" s="2">
+      <c r="O55" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>20</v>
@@ -8666,7 +8665,7 @@
         <v>20</v>
       </c>
       <c r="S55" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="T55" t="s" s="2">
         <v>20</v>
@@ -8705,7 +8704,7 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8723,10 +8722,10 @@
         <v>20</v>
       </c>
       <c r="AL55" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="AM55" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>319</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>20</v>
@@ -8737,10 +8736,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8766,13 +8765,13 @@
         <v>157</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>323</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8822,7 +8821,7 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8840,10 +8839,10 @@
         <v>20</v>
       </c>
       <c r="AL56" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="AM56" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>20</v>
@@ -8854,10 +8853,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8883,14 +8882,14 @@
         <v>109</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>329</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>20</v>
@@ -8939,7 +8938,7 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8957,10 +8956,10 @@
         <v>20</v>
       </c>
       <c r="AL57" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="AM57" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>20</v>
@@ -8971,10 +8970,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9000,14 +8999,14 @@
         <v>157</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>20</v>
@@ -9056,7 +9055,7 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -9074,10 +9073,10 @@
         <v>20</v>
       </c>
       <c r="AL58" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="AM58" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>341</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>20</v>
@@ -9088,10 +9087,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9114,19 +9113,19 @@
         <v>90</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="N59" t="s" s="2">
+      <c r="O59" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>20</v>
@@ -9175,7 +9174,7 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -9193,10 +9192,10 @@
         <v>20</v>
       </c>
       <c r="AL59" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AM59" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>20</v>
@@ -9207,13 +9206,13 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D60" t="s" s="2">
         <v>20</v>
@@ -9232,7 +9231,7 @@
         <v>20</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="K60" t="s" s="2">
         <v>297</v>
@@ -9276,7 +9275,7 @@
       </c>
       <c r="Y60" s="2"/>
       <c r="Z60" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>20</v>
@@ -9303,7 +9302,7 @@
         <v>80</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>303</v>
+        <v>20</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>101</v>
@@ -9312,10 +9311,10 @@
         <v>20</v>
       </c>
       <c r="AL60" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AM60" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>20</v>
@@ -9326,10 +9325,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9358,7 +9357,7 @@
         <v>292</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9441,10 +9440,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9473,10 +9472,10 @@
         <v>295</v>
       </c>
       <c r="M62" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="N62" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>310</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9558,10 +9557,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9587,16 +9586,16 @@
         <v>103</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="N63" t="s" s="2">
+      <c r="O63" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>20</v>
@@ -9606,7 +9605,7 @@
         <v>20</v>
       </c>
       <c r="S63" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="T63" t="s" s="2">
         <v>20</v>
@@ -9645,7 +9644,7 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9663,10 +9662,10 @@
         <v>20</v>
       </c>
       <c r="AL63" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="AM63" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>319</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>20</v>
@@ -9677,10 +9676,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9706,13 +9705,13 @@
         <v>157</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>323</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9762,7 +9761,7 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9780,10 +9779,10 @@
         <v>20</v>
       </c>
       <c r="AL64" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="AM64" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>20</v>
@@ -9794,10 +9793,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9823,14 +9822,14 @@
         <v>109</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>329</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>20</v>
@@ -9879,7 +9878,7 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9897,10 +9896,10 @@
         <v>20</v>
       </c>
       <c r="AL65" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="AM65" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>20</v>
@@ -9911,10 +9910,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9940,14 +9939,14 @@
         <v>157</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>20</v>
@@ -9996,7 +9995,7 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -10014,10 +10013,10 @@
         <v>20</v>
       </c>
       <c r="AL66" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="AM66" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="AM66" t="s" s="2">
-        <v>341</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>20</v>
@@ -10028,10 +10027,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10054,19 +10053,19 @@
         <v>90</v>
       </c>
       <c r="K67" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="L67" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="L67" t="s" s="2">
+      <c r="M67" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="M67" t="s" s="2">
+      <c r="N67" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="N67" t="s" s="2">
+      <c r="O67" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>20</v>
@@ -10115,7 +10114,7 @@
         <v>20</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -10133,10 +10132,10 @@
         <v>20</v>
       </c>
       <c r="AL67" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AM67" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="AM67" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>20</v>
@@ -10147,10 +10146,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10176,16 +10175,16 @@
         <v>157</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="M68" t="s" s="2">
+      <c r="N68" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="N68" t="s" s="2">
+      <c r="O68" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>20</v>
@@ -10234,7 +10233,7 @@
         <v>20</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -10252,10 +10251,10 @@
         <v>20</v>
       </c>
       <c r="AL68" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AM68" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>20</v>
@@ -10266,14 +10265,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -10295,13 +10294,13 @@
         <v>179</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10330,10 +10329,10 @@
         <v>285</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>20</v>
@@ -10351,7 +10350,7 @@
         <v>20</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -10360,7 +10359,7 @@
         <v>80</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>101</v>
@@ -10369,16 +10368,16 @@
         <v>20</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>449</v>
+        <v>389</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>450</v>
+        <v>391</v>
       </c>
     </row>
     <row r="70" hidden="true">
@@ -10486,7 +10485,7 @@
         <v>20</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>456</v>
@@ -12457,7 +12456,7 @@
         <v>598</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>599</v>
@@ -12572,7 +12571,7 @@
         <v>20</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>604</v>

--- a/docs/StructureDefinition-PASportServiceRequest.xlsx
+++ b/docs/StructureDefinition-PASportServiceRequest.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T13:32:15+08:00</t>
+    <t>2026-04-03T21:17:06+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PASportServiceRequest.xlsx
+++ b/docs/StructureDefinition-PASportServiceRequest.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-03T21:17:06+08:00</t>
+    <t>2026-06-25T08:48:04+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
